--- a/backend/data/financials_by_company/067280.KQ.xlsx
+++ b/backend/data/financials_by_company/067280.KQ.xlsx
@@ -687,632 +687,632 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-133550627.242191</v>
+        <v>87305595.38276701</v>
       </c>
       <c r="C2" t="n">
-        <v>0.262765</v>
+        <v>0.238793</v>
       </c>
       <c r="D2" t="n">
-        <v>64806546600</v>
+        <v>47692249220</v>
       </c>
       <c r="E2" t="n">
-        <v>-508251000</v>
+        <v>365612000</v>
       </c>
       <c r="F2" t="n">
-        <v>-508251000</v>
+        <v>365612000</v>
       </c>
       <c r="G2" t="n">
-        <v>31065766110</v>
+        <v>20379818130</v>
       </c>
       <c r="H2" t="n">
-        <v>20042220000</v>
+        <v>20245627000</v>
       </c>
       <c r="I2" t="n">
-        <v>251566227760</v>
+        <v>227077915540</v>
       </c>
       <c r="J2" t="n">
-        <v>64298295600</v>
+        <v>48057861220</v>
       </c>
       <c r="K2" t="n">
-        <v>44256075600</v>
+        <v>27812234220</v>
       </c>
       <c r="L2" t="n">
-        <v>4456344850</v>
+        <v>-164910270</v>
       </c>
       <c r="M2" t="n">
-        <v>1510789000</v>
+        <v>807402000</v>
       </c>
       <c r="N2" t="n">
-        <v>5967134000</v>
+        <v>642492000</v>
       </c>
       <c r="O2" t="n">
-        <v>31440466482.75781</v>
+        <v>20101511725.38277</v>
       </c>
       <c r="P2" t="n">
-        <v>31065766110</v>
+        <v>20379818130</v>
       </c>
       <c r="Q2" t="n">
-        <v>313810670760</v>
+        <v>281673368540</v>
       </c>
       <c r="R2" t="n">
-        <v>1344943000</v>
+        <v>1524391000</v>
       </c>
       <c r="S2" t="n">
-        <v>38928839410</v>
+        <v>26467125550</v>
       </c>
       <c r="T2" t="n">
-        <v>5926319</v>
+        <v>5926088</v>
       </c>
       <c r="U2" t="n">
-        <v>5926319</v>
+        <v>5926088</v>
       </c>
       <c r="V2" t="n">
-        <v>5242</v>
+        <v>3439</v>
       </c>
       <c r="W2" t="n">
-        <v>5242</v>
+        <v>3439</v>
       </c>
       <c r="X2" t="n">
-        <v>31065766110</v>
+        <v>20379818130</v>
       </c>
       <c r="Y2" t="n">
-        <v>31065766110</v>
+        <v>20379818130</v>
       </c>
       <c r="Z2" t="n">
-        <v>-447550780</v>
+        <v>-176448510</v>
       </c>
       <c r="AA2" t="n">
-        <v>31513316890</v>
+        <v>20556266640</v>
       </c>
       <c r="AB2" t="n">
-        <v>31513316890</v>
+        <v>20556266640</v>
       </c>
       <c r="AC2" t="n">
-        <v>11231969710</v>
+        <v>6448565570</v>
       </c>
       <c r="AD2" t="n">
-        <v>42745286600</v>
+        <v>27004832220</v>
       </c>
       <c r="AE2" t="n">
-        <v>202876000</v>
+        <v>425086000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-513614000</v>
+        <v>361014000</v>
       </c>
       <c r="AG2" t="n">
-        <v>513614000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
+        <v>21490000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-382504000</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>4456344850</v>
+        <v>-164910270</v>
       </c>
       <c r="AK2" t="n">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="AL2" t="n">
-        <v>1510789000</v>
+        <v>807402000</v>
       </c>
       <c r="AM2" t="n">
-        <v>5967134000</v>
+        <v>642492000</v>
       </c>
       <c r="AN2" t="n">
-        <v>38928838970</v>
+        <v>26608222910</v>
       </c>
       <c r="AO2" t="n">
-        <v>62244443000</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
+        <v>54595453000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-141097000</v>
+      </c>
       <c r="AQ2" t="n">
-        <v>2115136000</v>
+        <v>3608164000</v>
       </c>
       <c r="AR2" t="n">
-        <v>53025000</v>
+        <v>740396000</v>
       </c>
       <c r="AS2" t="n">
-        <v>2062111000</v>
+        <v>2867768000</v>
       </c>
       <c r="AT2" t="n">
-        <v>7884169000</v>
+        <v>6083721000</v>
       </c>
       <c r="AU2" t="n">
-        <v>3775804000</v>
+        <v>3823637000</v>
       </c>
       <c r="AV2" t="n">
-        <v>4108365000</v>
+        <v>2260084000</v>
       </c>
       <c r="AW2" t="n">
-        <v>1344943000</v>
+        <v>1524391000</v>
       </c>
       <c r="AX2" t="n">
-        <v>101173281970</v>
+        <v>81203675910</v>
       </c>
       <c r="AY2" t="n">
-        <v>251566227760</v>
+        <v>227077915540</v>
       </c>
       <c r="AZ2" t="n">
-        <v>352739509730</v>
+        <v>308281591450</v>
       </c>
       <c r="BA2" t="n">
-        <v>352739509730</v>
+        <v>308281591450</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-131217974.87128</v>
+        <v>-78486869.35720199</v>
       </c>
       <c r="C3" t="n">
-        <v>0.243561</v>
+        <v>0.262791</v>
       </c>
       <c r="D3" t="n">
-        <v>63013880210</v>
+        <v>63746467340</v>
       </c>
       <c r="E3" t="n">
-        <v>-538748000</v>
+        <v>-298667000</v>
       </c>
       <c r="F3" t="n">
-        <v>-538748000</v>
+        <v>-298667000</v>
       </c>
       <c r="G3" t="n">
-        <v>31507268860</v>
+        <v>30259194090</v>
       </c>
       <c r="H3" t="n">
-        <v>18524512000</v>
+        <v>20739084000</v>
       </c>
       <c r="I3" t="n">
-        <v>258221204350</v>
+        <v>258027588980</v>
       </c>
       <c r="J3" t="n">
-        <v>62475132210</v>
+        <v>63447800340</v>
       </c>
       <c r="K3" t="n">
-        <v>43950620210</v>
+        <v>42708716340</v>
       </c>
       <c r="L3" t="n">
-        <v>2833007690</v>
+        <v>601473190</v>
       </c>
       <c r="M3" t="n">
-        <v>1726187000</v>
+        <v>1282684000</v>
       </c>
       <c r="N3" t="n">
-        <v>4559194000</v>
+        <v>1884157000</v>
       </c>
       <c r="O3" t="n">
-        <v>31914798885.12872</v>
+        <v>30479374220.6428</v>
       </c>
       <c r="P3" t="n">
-        <v>31507268860</v>
+        <v>30259194090</v>
       </c>
       <c r="Q3" t="n">
-        <v>318307829350</v>
+        <v>316317590980</v>
       </c>
       <c r="R3" t="n">
-        <v>1323097000</v>
+        <v>1478129000</v>
       </c>
       <c r="S3" t="n">
-        <v>40285830660</v>
+        <v>41042292160</v>
       </c>
       <c r="T3" t="n">
-        <v>5926875</v>
+        <v>5926203</v>
       </c>
       <c r="U3" t="n">
-        <v>5926875</v>
+        <v>5926203</v>
       </c>
       <c r="V3" t="n">
-        <v>5316</v>
+        <v>5106</v>
       </c>
       <c r="W3" t="n">
-        <v>5316</v>
+        <v>5106</v>
       </c>
       <c r="X3" t="n">
-        <v>31507268860</v>
+        <v>30259194090</v>
       </c>
       <c r="Y3" t="n">
-        <v>31507268860</v>
+        <v>30259194090</v>
       </c>
       <c r="Z3" t="n">
-        <v>-432941260</v>
+        <v>-280467840</v>
       </c>
       <c r="AA3" t="n">
-        <v>31940210130</v>
+        <v>30539661940</v>
       </c>
       <c r="AB3" t="n">
-        <v>31940210130</v>
+        <v>30539661940</v>
       </c>
       <c r="AC3" t="n">
-        <v>10284223080</v>
+        <v>10886370400</v>
       </c>
       <c r="AD3" t="n">
-        <v>42224433210</v>
+        <v>41426032340</v>
       </c>
       <c r="AE3" t="n">
-        <v>-405378000</v>
+        <v>135578000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-544481000</v>
+        <v>-304703000</v>
       </c>
       <c r="AG3" t="n">
-        <v>544481000</v>
+        <v>304703000</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>2833007690</v>
+        <v>601473190</v>
       </c>
       <c r="AK3" t="n">
-        <v>-690</v>
+        <v>-190</v>
       </c>
       <c r="AL3" t="n">
-        <v>1726187000</v>
+        <v>1282684000</v>
       </c>
       <c r="AM3" t="n">
-        <v>4559194000</v>
+        <v>1884157000</v>
       </c>
       <c r="AN3" t="n">
-        <v>40290422070</v>
+        <v>41169256920</v>
       </c>
       <c r="AO3" t="n">
-        <v>60086625000</v>
+        <v>58290002000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-4591000</v>
+        <v>-126964000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2542476000</v>
+        <v>3354424000</v>
       </c>
       <c r="AR3" t="n">
-        <v>455202000</v>
+        <v>470039000</v>
       </c>
       <c r="AS3" t="n">
-        <v>2087274000</v>
+        <v>2884385000</v>
       </c>
       <c r="AT3" t="n">
-        <v>7614925000</v>
+        <v>6752781000</v>
       </c>
       <c r="AU3" t="n">
-        <v>3618587000</v>
+        <v>3111097000</v>
       </c>
       <c r="AV3" t="n">
-        <v>3996338000</v>
+        <v>3641684000</v>
       </c>
       <c r="AW3" t="n">
-        <v>1323097000</v>
+        <v>1478129000</v>
       </c>
       <c r="AX3" t="n">
-        <v>100377047070</v>
+        <v>99459258920</v>
       </c>
       <c r="AY3" t="n">
-        <v>258221204350</v>
+        <v>258027588980</v>
       </c>
       <c r="AZ3" t="n">
-        <v>358598251420</v>
+        <v>357486847900</v>
       </c>
       <c r="BA3" t="n">
-        <v>358598251420</v>
+        <v>357486847900</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-78486869.35720199</v>
+        <v>-131217974.87128</v>
       </c>
       <c r="C4" t="n">
-        <v>0.262791</v>
+        <v>0.243561</v>
       </c>
       <c r="D4" t="n">
-        <v>63746467340</v>
+        <v>63013880210</v>
       </c>
       <c r="E4" t="n">
-        <v>-298667000</v>
+        <v>-538748000</v>
       </c>
       <c r="F4" t="n">
-        <v>-298667000</v>
+        <v>-538748000</v>
       </c>
       <c r="G4" t="n">
-        <v>30259194090</v>
+        <v>31507268860</v>
       </c>
       <c r="H4" t="n">
-        <v>20739084000</v>
+        <v>18524512000</v>
       </c>
       <c r="I4" t="n">
-        <v>258027588980</v>
+        <v>258221204350</v>
       </c>
       <c r="J4" t="n">
-        <v>63447800340</v>
+        <v>62475132210</v>
       </c>
       <c r="K4" t="n">
-        <v>42708716340</v>
+        <v>43950620210</v>
       </c>
       <c r="L4" t="n">
-        <v>601473190</v>
+        <v>2833007690</v>
       </c>
       <c r="M4" t="n">
-        <v>1282684000</v>
+        <v>1726187000</v>
       </c>
       <c r="N4" t="n">
-        <v>1884157000</v>
+        <v>4559194000</v>
       </c>
       <c r="O4" t="n">
-        <v>30479374220.6428</v>
+        <v>31914798885.12872</v>
       </c>
       <c r="P4" t="n">
-        <v>30259194090</v>
+        <v>31507268860</v>
       </c>
       <c r="Q4" t="n">
-        <v>316317590980</v>
+        <v>318307829350</v>
       </c>
       <c r="R4" t="n">
-        <v>1478129000</v>
+        <v>1323097000</v>
       </c>
       <c r="S4" t="n">
-        <v>41042292160</v>
+        <v>40285830660</v>
       </c>
       <c r="T4" t="n">
-        <v>5926203</v>
+        <v>5926875</v>
       </c>
       <c r="U4" t="n">
-        <v>5926203</v>
+        <v>5926875</v>
       </c>
       <c r="V4" t="n">
-        <v>5106</v>
+        <v>5316</v>
       </c>
       <c r="W4" t="n">
-        <v>5106</v>
+        <v>5316</v>
       </c>
       <c r="X4" t="n">
-        <v>30259194090</v>
+        <v>31507268860</v>
       </c>
       <c r="Y4" t="n">
-        <v>30259194090</v>
+        <v>31507268860</v>
       </c>
       <c r="Z4" t="n">
-        <v>-280467840</v>
+        <v>-432941260</v>
       </c>
       <c r="AA4" t="n">
-        <v>30539661940</v>
+        <v>31940210130</v>
       </c>
       <c r="AB4" t="n">
-        <v>30539661940</v>
+        <v>31940210130</v>
       </c>
       <c r="AC4" t="n">
-        <v>10886370400</v>
+        <v>10284223080</v>
       </c>
       <c r="AD4" t="n">
-        <v>41426032340</v>
+        <v>42224433210</v>
       </c>
       <c r="AE4" t="n">
-        <v>135578000</v>
+        <v>-405378000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-304703000</v>
+        <v>-544481000</v>
       </c>
       <c r="AG4" t="n">
-        <v>304703000</v>
+        <v>544481000</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>601473190</v>
+        <v>2833007690</v>
       </c>
       <c r="AK4" t="n">
-        <v>-190</v>
+        <v>-690</v>
       </c>
       <c r="AL4" t="n">
-        <v>1282684000</v>
+        <v>1726187000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1884157000</v>
+        <v>4559194000</v>
       </c>
       <c r="AN4" t="n">
-        <v>41169256920</v>
+        <v>40290422070</v>
       </c>
       <c r="AO4" t="n">
-        <v>58290002000</v>
+        <v>60086625000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-126964000</v>
+        <v>-4591000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3354424000</v>
+        <v>2542476000</v>
       </c>
       <c r="AR4" t="n">
-        <v>470039000</v>
+        <v>455202000</v>
       </c>
       <c r="AS4" t="n">
-        <v>2884385000</v>
+        <v>2087274000</v>
       </c>
       <c r="AT4" t="n">
-        <v>6752781000</v>
+        <v>7614925000</v>
       </c>
       <c r="AU4" t="n">
-        <v>3111097000</v>
+        <v>3618587000</v>
       </c>
       <c r="AV4" t="n">
-        <v>3641684000</v>
+        <v>3996338000</v>
       </c>
       <c r="AW4" t="n">
-        <v>1478129000</v>
+        <v>1323097000</v>
       </c>
       <c r="AX4" t="n">
-        <v>99459258920</v>
+        <v>100377047070</v>
       </c>
       <c r="AY4" t="n">
-        <v>258027588980</v>
+        <v>258221204350</v>
       </c>
       <c r="AZ4" t="n">
-        <v>357486847900</v>
+        <v>358598251420</v>
       </c>
       <c r="BA4" t="n">
-        <v>357486847900</v>
+        <v>358598251420</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>87305595.38276701</v>
+        <v>-133550627.242191</v>
       </c>
       <c r="C5" t="n">
-        <v>0.238793</v>
+        <v>0.262765</v>
       </c>
       <c r="D5" t="n">
-        <v>47692249220</v>
+        <v>64806546600</v>
       </c>
       <c r="E5" t="n">
-        <v>365612000</v>
+        <v>-508251000</v>
       </c>
       <c r="F5" t="n">
-        <v>365612000</v>
+        <v>-508251000</v>
       </c>
       <c r="G5" t="n">
-        <v>20379818130</v>
+        <v>31065766110</v>
       </c>
       <c r="H5" t="n">
-        <v>20245627000</v>
+        <v>20042220000</v>
       </c>
       <c r="I5" t="n">
-        <v>227077915540</v>
+        <v>251566227760</v>
       </c>
       <c r="J5" t="n">
-        <v>48057861220</v>
+        <v>64298295600</v>
       </c>
       <c r="K5" t="n">
-        <v>27812234220</v>
+        <v>44256075600</v>
       </c>
       <c r="L5" t="n">
-        <v>-164910270</v>
+        <v>4456344850</v>
       </c>
       <c r="M5" t="n">
-        <v>807402000</v>
+        <v>1510789000</v>
       </c>
       <c r="N5" t="n">
-        <v>642492000</v>
+        <v>5967134000</v>
       </c>
       <c r="O5" t="n">
-        <v>20101511725.38277</v>
+        <v>31440466482.75781</v>
       </c>
       <c r="P5" t="n">
-        <v>20379818130</v>
+        <v>31065766110</v>
       </c>
       <c r="Q5" t="n">
-        <v>281673368540</v>
+        <v>313810670760</v>
       </c>
       <c r="R5" t="n">
-        <v>1524391000</v>
+        <v>1344943000</v>
       </c>
       <c r="S5" t="n">
-        <v>26467125550</v>
+        <v>38928839410</v>
       </c>
       <c r="T5" t="n">
-        <v>5926088</v>
+        <v>5926319</v>
       </c>
       <c r="U5" t="n">
-        <v>5926088</v>
+        <v>5926319</v>
       </c>
       <c r="V5" t="n">
-        <v>3439</v>
+        <v>5242</v>
       </c>
       <c r="W5" t="n">
-        <v>3439</v>
+        <v>5242</v>
       </c>
       <c r="X5" t="n">
-        <v>20379818130</v>
+        <v>31065766110</v>
       </c>
       <c r="Y5" t="n">
-        <v>20379818130</v>
+        <v>31065766110</v>
       </c>
       <c r="Z5" t="n">
-        <v>-176448510</v>
+        <v>-447550780</v>
       </c>
       <c r="AA5" t="n">
-        <v>20556266640</v>
+        <v>31513316890</v>
       </c>
       <c r="AB5" t="n">
-        <v>20556266640</v>
+        <v>31513316890</v>
       </c>
       <c r="AC5" t="n">
-        <v>6448565570</v>
+        <v>11231969710</v>
       </c>
       <c r="AD5" t="n">
-        <v>27004832220</v>
+        <v>42745286600</v>
       </c>
       <c r="AE5" t="n">
-        <v>425086000</v>
+        <v>202876000</v>
       </c>
       <c r="AF5" t="n">
-        <v>361014000</v>
+        <v>-513614000</v>
       </c>
       <c r="AG5" t="n">
-        <v>21490000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-382504000</v>
-      </c>
+        <v>513614000</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>-164910270</v>
+        <v>4456344850</v>
       </c>
       <c r="AK5" t="n">
-        <v>270</v>
+        <v>150</v>
       </c>
       <c r="AL5" t="n">
-        <v>807402000</v>
+        <v>1510789000</v>
       </c>
       <c r="AM5" t="n">
-        <v>642492000</v>
+        <v>5967134000</v>
       </c>
       <c r="AN5" t="n">
-        <v>26608222910</v>
+        <v>38928838970</v>
       </c>
       <c r="AO5" t="n">
-        <v>54595453000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-141097000</v>
-      </c>
+        <v>62244443000</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>3608164000</v>
+        <v>2115136000</v>
       </c>
       <c r="AR5" t="n">
-        <v>740396000</v>
+        <v>53025000</v>
       </c>
       <c r="AS5" t="n">
-        <v>2867768000</v>
+        <v>2062111000</v>
       </c>
       <c r="AT5" t="n">
-        <v>6083721000</v>
+        <v>7884169000</v>
       </c>
       <c r="AU5" t="n">
-        <v>3823637000</v>
+        <v>3775804000</v>
       </c>
       <c r="AV5" t="n">
-        <v>2260084000</v>
+        <v>4108365000</v>
       </c>
       <c r="AW5" t="n">
-        <v>1524391000</v>
+        <v>1344943000</v>
       </c>
       <c r="AX5" t="n">
-        <v>81203675910</v>
+        <v>101173281970</v>
       </c>
       <c r="AY5" t="n">
-        <v>227077915540</v>
+        <v>251566227760</v>
       </c>
       <c r="AZ5" t="n">
-        <v>308281591450</v>
+        <v>352739509730</v>
       </c>
       <c r="BA5" t="n">
-        <v>308281591450</v>
+        <v>352739509730</v>
       </c>
     </row>
   </sheetData>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -1668,187 +1668,187 @@
         <v>5926779</v>
       </c>
       <c r="F2" t="n">
-        <v>37309646160</v>
+        <v>50896469650</v>
       </c>
       <c r="G2" t="n">
-        <v>181876811300</v>
+        <v>97398188030</v>
       </c>
       <c r="H2" t="n">
-        <v>216256668300</v>
+        <v>137156937030</v>
       </c>
       <c r="I2" t="n">
-        <v>162007174800</v>
+        <v>62761011530</v>
       </c>
       <c r="J2" t="n">
-        <v>181876811300</v>
+        <v>97398188030</v>
       </c>
       <c r="K2" t="n">
-        <v>37309646160</v>
+        <v>50896469650</v>
       </c>
       <c r="L2" t="n">
-        <v>216256668300</v>
+        <v>137156937030</v>
       </c>
       <c r="M2" t="n">
-        <v>216256668300</v>
+        <v>137156937030</v>
       </c>
       <c r="N2" t="n">
-        <v>221027496030</v>
+        <v>139966656420</v>
       </c>
       <c r="O2" t="n">
-        <v>4770827730</v>
+        <v>2809719390</v>
       </c>
       <c r="P2" t="n">
-        <v>216256668300</v>
+        <v>137156937030</v>
       </c>
       <c r="Q2" t="n">
-        <v>-60</v>
+        <v>-560</v>
       </c>
       <c r="R2" t="n">
-        <v>234477845710</v>
+        <v>159425953630</v>
       </c>
       <c r="S2" t="n">
         <v>41951673000</v>
       </c>
       <c r="T2" t="n">
-        <v>2963389500</v>
+        <v>2963390000</v>
       </c>
       <c r="U2" t="n">
-        <v>2963389500</v>
+        <v>2963390000</v>
       </c>
       <c r="V2" t="n">
-        <v>99690002910</v>
+        <v>117016269800</v>
       </c>
       <c r="W2" t="n">
-        <v>31939387280</v>
+        <v>44569787010</v>
       </c>
       <c r="X2" t="n">
         <v>10</v>
       </c>
       <c r="Y2" t="n">
-        <v>1330218500</v>
+        <v>620820830</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>1206872990</v>
+        <v>284466260</v>
       </c>
       <c r="AB2" t="n">
-        <v>25860205980</v>
+        <v>40607907910</v>
       </c>
       <c r="AC2" t="n">
-        <v>25860205980</v>
+        <v>40607907910</v>
       </c>
       <c r="AD2" t="n">
-        <v>3542089800</v>
+        <v>3056592000</v>
       </c>
       <c r="AE2" t="n">
-        <v>67750615630</v>
+        <v>72446482790</v>
       </c>
       <c r="AF2" t="n">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="AG2" t="n">
-        <v>11449440180</v>
+        <v>10288561740</v>
       </c>
       <c r="AH2" t="n">
-        <v>11449440180</v>
+        <v>10288561740</v>
       </c>
       <c r="AI2" t="n">
-        <v>87798880</v>
+        <v>293334860</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25936488820</v>
+        <v>18968334810</v>
       </c>
       <c r="AK2" t="n">
-        <v>1463567360</v>
+        <v>1059892580</v>
       </c>
       <c r="AL2" t="n">
-        <v>10487924460</v>
+        <v>6365469920</v>
       </c>
       <c r="AM2" t="n">
-        <v>13984997000</v>
+        <v>11542972310</v>
       </c>
       <c r="AN2" t="n">
-        <v>320717498950</v>
+        <v>256982926230</v>
       </c>
       <c r="AO2" t="n">
-        <v>90959708520</v>
+        <v>121775431900</v>
       </c>
       <c r="AP2" t="n">
-        <v>-640</v>
+        <v>120</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6416180630</v>
+        <v>2474530210</v>
       </c>
       <c r="AR2" t="n">
-        <v>3360223170</v>
+        <v>1663763620</v>
       </c>
       <c r="AS2" t="n">
-        <v>1236365280</v>
+        <v>1219233130</v>
       </c>
       <c r="AT2" t="n">
-        <v>1236365280</v>
+        <v>1219233130</v>
       </c>
       <c r="AU2" t="n">
-        <v>34379857000</v>
+        <v>39758749000</v>
       </c>
       <c r="AV2" t="n">
-        <v>20224268000</v>
+        <v>26628254000</v>
       </c>
       <c r="AW2" t="n">
-        <v>14155589000</v>
+        <v>13130495000</v>
       </c>
       <c r="AX2" t="n">
-        <v>35650439130</v>
+        <v>56494905550</v>
       </c>
       <c r="AY2" t="n">
-        <v>-45007409000</v>
+        <v>-32041564000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>80657848000</v>
+        <v>88536470000</v>
       </c>
       <c r="BA2" t="n">
-        <v>73858929000</v>
+        <v>73308129000</v>
       </c>
       <c r="BB2" t="n">
-        <v>6798919000</v>
+        <v>15228341000</v>
       </c>
       <c r="BC2" t="n">
-        <v>229757790430</v>
+        <v>135207494320</v>
       </c>
       <c r="BD2" t="n">
-        <v>-330</v>
+        <v>1070</v>
       </c>
       <c r="BE2" t="n">
-        <v>3651935070</v>
+        <v>1188013670</v>
       </c>
       <c r="BF2" t="n">
-        <v>18583127000</v>
+        <v>24173170740</v>
       </c>
       <c r="BG2" t="n">
-        <v>40481461000</v>
+        <v>41670740000</v>
       </c>
       <c r="BH2" t="n">
-        <v>-66463000</v>
+        <v>-13404000</v>
       </c>
       <c r="BI2" t="n">
-        <v>40547924000</v>
+        <v>41684144000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>167041267690</v>
+        <v>68175568840</v>
       </c>
       <c r="BK2" t="n">
-        <v>144258200000</v>
+        <v>39835690460</v>
       </c>
       <c r="BL2" t="n">
-        <v>22783067690</v>
+        <v>28339878380</v>
       </c>
       <c r="BM2" t="n">
-        <v>22783068000</v>
+        <v>28339878000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -1863,43 +1863,43 @@
         <v>5926779</v>
       </c>
       <c r="F3" t="n">
-        <v>45946401910</v>
+        <v>51958475200</v>
       </c>
       <c r="G3" t="n">
-        <v>163529373850</v>
+        <v>134157694240</v>
       </c>
       <c r="H3" t="n">
-        <v>193621892850</v>
+        <v>169091910240</v>
       </c>
       <c r="I3" t="n">
-        <v>136600185370</v>
+        <v>97355312280</v>
       </c>
       <c r="J3" t="n">
-        <v>163529373850</v>
+        <v>134157694240</v>
       </c>
       <c r="K3" t="n">
-        <v>45946401910</v>
+        <v>51958475200</v>
       </c>
       <c r="L3" t="n">
-        <v>193621892850</v>
+        <v>169091910240</v>
       </c>
       <c r="M3" t="n">
-        <v>193621892850</v>
+        <v>169091910240</v>
       </c>
       <c r="N3" t="n">
-        <v>197384602590</v>
+        <v>172369983990</v>
       </c>
       <c r="O3" t="n">
-        <v>3762709730</v>
+        <v>3278073740</v>
       </c>
       <c r="P3" t="n">
-        <v>193621892850</v>
+        <v>169091910240</v>
       </c>
       <c r="Q3" t="n">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="R3" t="n">
-        <v>212894925990</v>
+        <v>186129080330</v>
       </c>
       <c r="S3" t="n">
         <v>41951673000</v>
@@ -1911,141 +1911,139 @@
         <v>2963389500</v>
       </c>
       <c r="V3" t="n">
-        <v>114400645170</v>
+        <v>119379682770</v>
       </c>
       <c r="W3" t="n">
-        <v>40361597690</v>
+        <v>48527445740</v>
       </c>
       <c r="X3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="n">
-        <v>1181161530</v>
+        <v>658323310</v>
       </c>
       <c r="Z3" t="n">
-        <v>48770700</v>
+        <v>97675030</v>
       </c>
       <c r="AA3" t="n">
-        <v>987238920</v>
+        <v>1381310150</v>
       </c>
       <c r="AB3" t="n">
-        <v>34778871540</v>
+        <v>42733775150</v>
       </c>
       <c r="AC3" t="n">
-        <v>34778871540</v>
+        <v>42733775150</v>
       </c>
       <c r="AD3" t="n">
-        <v>3365554970</v>
+        <v>3656362080</v>
       </c>
       <c r="AE3" t="n">
-        <v>74039047470</v>
+        <v>70852237020</v>
       </c>
       <c r="AF3" t="n">
-        <v>40</v>
+        <v>280</v>
       </c>
       <c r="AG3" t="n">
-        <v>11167530370</v>
+        <v>9224700050</v>
       </c>
       <c r="AH3" t="n">
-        <v>11167530370</v>
+        <v>9224700050</v>
       </c>
       <c r="AI3" t="n">
-        <v>319835370</v>
+        <v>286926240</v>
       </c>
       <c r="AJ3" t="n">
-        <v>23536524400</v>
+        <v>24349715950</v>
       </c>
       <c r="AK3" t="n">
-        <v>1610113620</v>
+        <v>1068171040</v>
       </c>
       <c r="AL3" t="n">
-        <v>10206584780</v>
+        <v>7980137290</v>
       </c>
       <c r="AM3" t="n">
-        <v>11719826000</v>
+        <v>15301407620</v>
       </c>
       <c r="AN3" t="n">
-        <v>311785247760</v>
+        <v>291749666760</v>
       </c>
       <c r="AO3" t="n">
-        <v>101146014910</v>
+        <v>123542117460</v>
       </c>
       <c r="AP3" t="n">
-        <v>560</v>
+        <v>-410</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10294218160</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1691818380</v>
-      </c>
+        <v>16165963800</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>1231002470</v>
+        <v>1225268770</v>
       </c>
       <c r="AT3" t="n">
-        <v>1231002470</v>
+        <v>1225268770</v>
       </c>
       <c r="AU3" t="n">
-        <v>30092519000</v>
+        <v>34934216000</v>
       </c>
       <c r="AV3" t="n">
-        <v>16587658000</v>
+        <v>21508984000</v>
       </c>
       <c r="AW3" t="n">
-        <v>13504861000</v>
+        <v>13425232000</v>
       </c>
       <c r="AX3" t="n">
-        <v>45660511920</v>
+        <v>55285581090</v>
       </c>
       <c r="AY3" t="n">
-        <v>-35673683000</v>
+        <v>-32317581000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>81334195000</v>
+        <v>87603162000</v>
       </c>
       <c r="BA3" t="n">
-        <v>73777130000</v>
+        <v>72508837000</v>
       </c>
       <c r="BB3" t="n">
-        <v>7557065000</v>
+        <v>15094325000</v>
       </c>
       <c r="BC3" t="n">
-        <v>210639232840</v>
+        <v>168207549300</v>
       </c>
       <c r="BD3" t="n">
-        <v>-170</v>
+        <v>-430</v>
       </c>
       <c r="BE3" t="n">
-        <v>1971382580</v>
+        <v>1415887110</v>
       </c>
       <c r="BF3" t="n">
-        <v>19982039000</v>
+        <v>30864959820</v>
       </c>
       <c r="BG3" t="n">
-        <v>39700469000</v>
+        <v>31680318000</v>
       </c>
       <c r="BH3" t="n">
-        <v>-63772000</v>
+        <v>-23056000</v>
       </c>
       <c r="BI3" t="n">
-        <v>39764241000</v>
+        <v>31703374000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>148985342430</v>
+        <v>104246384800</v>
       </c>
       <c r="BK3" t="n">
-        <v>115522500200</v>
+        <v>69979221700</v>
       </c>
       <c r="BL3" t="n">
-        <v>33462842230</v>
+        <v>34267163100</v>
       </c>
       <c r="BM3" t="n">
-        <v>33462842000</v>
+        <v>34267163000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -2060,43 +2058,43 @@
         <v>5926779</v>
       </c>
       <c r="F4" t="n">
-        <v>51958475200</v>
+        <v>45946401910</v>
       </c>
       <c r="G4" t="n">
-        <v>134157694240</v>
+        <v>163529373850</v>
       </c>
       <c r="H4" t="n">
-        <v>169091910240</v>
+        <v>193621892850</v>
       </c>
       <c r="I4" t="n">
-        <v>97355312280</v>
+        <v>136600185370</v>
       </c>
       <c r="J4" t="n">
-        <v>134157694240</v>
+        <v>163529373850</v>
       </c>
       <c r="K4" t="n">
-        <v>51958475200</v>
+        <v>45946401910</v>
       </c>
       <c r="L4" t="n">
-        <v>169091910240</v>
+        <v>193621892850</v>
       </c>
       <c r="M4" t="n">
-        <v>169091910240</v>
+        <v>193621892850</v>
       </c>
       <c r="N4" t="n">
-        <v>172369983990</v>
+        <v>197384602590</v>
       </c>
       <c r="O4" t="n">
-        <v>3278073740</v>
+        <v>3762709730</v>
       </c>
       <c r="P4" t="n">
-        <v>169091910240</v>
+        <v>193621892850</v>
       </c>
       <c r="Q4" t="n">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="R4" t="n">
-        <v>186129080330</v>
+        <v>212894925990</v>
       </c>
       <c r="S4" t="n">
         <v>41951673000</v>
@@ -2108,139 +2106,141 @@
         <v>2963389500</v>
       </c>
       <c r="V4" t="n">
-        <v>119379682770</v>
+        <v>114400645170</v>
       </c>
       <c r="W4" t="n">
-        <v>48527445740</v>
+        <v>40361597690</v>
       </c>
       <c r="X4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="Y4" t="n">
-        <v>658323310</v>
+        <v>1181161530</v>
       </c>
       <c r="Z4" t="n">
-        <v>97675030</v>
+        <v>48770700</v>
       </c>
       <c r="AA4" t="n">
-        <v>1381310150</v>
+        <v>987238920</v>
       </c>
       <c r="AB4" t="n">
-        <v>42733775150</v>
+        <v>34778871540</v>
       </c>
       <c r="AC4" t="n">
-        <v>42733775150</v>
+        <v>34778871540</v>
       </c>
       <c r="AD4" t="n">
-        <v>3656362080</v>
+        <v>3365554970</v>
       </c>
       <c r="AE4" t="n">
-        <v>70852237020</v>
+        <v>74039047470</v>
       </c>
       <c r="AF4" t="n">
-        <v>280</v>
+        <v>40</v>
       </c>
       <c r="AG4" t="n">
-        <v>9224700050</v>
+        <v>11167530370</v>
       </c>
       <c r="AH4" t="n">
-        <v>9224700050</v>
+        <v>11167530370</v>
       </c>
       <c r="AI4" t="n">
-        <v>286926240</v>
+        <v>319835370</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24349715950</v>
+        <v>23536524400</v>
       </c>
       <c r="AK4" t="n">
-        <v>1068171040</v>
+        <v>1610113620</v>
       </c>
       <c r="AL4" t="n">
-        <v>7980137290</v>
+        <v>10206584780</v>
       </c>
       <c r="AM4" t="n">
-        <v>15301407620</v>
+        <v>11719826000</v>
       </c>
       <c r="AN4" t="n">
-        <v>291749666760</v>
+        <v>311785247760</v>
       </c>
       <c r="AO4" t="n">
-        <v>123542117460</v>
+        <v>101146014910</v>
       </c>
       <c r="AP4" t="n">
-        <v>-410</v>
+        <v>560</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16165963800</v>
-      </c>
-      <c r="AR4" t="inlineStr"/>
+        <v>10294218160</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1691818380</v>
+      </c>
       <c r="AS4" t="n">
-        <v>1225268770</v>
+        <v>1231002470</v>
       </c>
       <c r="AT4" t="n">
-        <v>1225268770</v>
+        <v>1231002470</v>
       </c>
       <c r="AU4" t="n">
-        <v>34934216000</v>
+        <v>30092519000</v>
       </c>
       <c r="AV4" t="n">
-        <v>21508984000</v>
+        <v>16587658000</v>
       </c>
       <c r="AW4" t="n">
-        <v>13425232000</v>
+        <v>13504861000</v>
       </c>
       <c r="AX4" t="n">
-        <v>55285581090</v>
+        <v>45660511920</v>
       </c>
       <c r="AY4" t="n">
-        <v>-32317581000</v>
+        <v>-35673683000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>87603162000</v>
+        <v>81334195000</v>
       </c>
       <c r="BA4" t="n">
-        <v>72508837000</v>
+        <v>73777130000</v>
       </c>
       <c r="BB4" t="n">
-        <v>15094325000</v>
+        <v>7557065000</v>
       </c>
       <c r="BC4" t="n">
-        <v>168207549300</v>
+        <v>210639232840</v>
       </c>
       <c r="BD4" t="n">
-        <v>-430</v>
+        <v>-170</v>
       </c>
       <c r="BE4" t="n">
-        <v>1415887110</v>
+        <v>1971382580</v>
       </c>
       <c r="BF4" t="n">
-        <v>30864959820</v>
+        <v>19982039000</v>
       </c>
       <c r="BG4" t="n">
-        <v>31680318000</v>
+        <v>39700469000</v>
       </c>
       <c r="BH4" t="n">
-        <v>-23056000</v>
+        <v>-63772000</v>
       </c>
       <c r="BI4" t="n">
-        <v>31703374000</v>
+        <v>39764241000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>104246384800</v>
+        <v>148985342430</v>
       </c>
       <c r="BK4" t="n">
-        <v>69979221700</v>
+        <v>115522500200</v>
       </c>
       <c r="BL4" t="n">
-        <v>34267163100</v>
+        <v>33462842230</v>
       </c>
       <c r="BM4" t="n">
-        <v>34267163000</v>
+        <v>33462842000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
@@ -2255,182 +2255,182 @@
         <v>5926779</v>
       </c>
       <c r="F5" t="n">
-        <v>50896469650</v>
+        <v>37309646160</v>
       </c>
       <c r="G5" t="n">
-        <v>97398188030</v>
+        <v>181876811300</v>
       </c>
       <c r="H5" t="n">
-        <v>137156937030</v>
+        <v>216256668300</v>
       </c>
       <c r="I5" t="n">
-        <v>62761011530</v>
+        <v>162007174800</v>
       </c>
       <c r="J5" t="n">
-        <v>97398188030</v>
+        <v>181876811300</v>
       </c>
       <c r="K5" t="n">
-        <v>50896469650</v>
+        <v>37309646160</v>
       </c>
       <c r="L5" t="n">
-        <v>137156937030</v>
+        <v>216256668300</v>
       </c>
       <c r="M5" t="n">
-        <v>137156937030</v>
+        <v>216256668300</v>
       </c>
       <c r="N5" t="n">
-        <v>139966656420</v>
+        <v>221027496030</v>
       </c>
       <c r="O5" t="n">
-        <v>2809719390</v>
+        <v>4770827730</v>
       </c>
       <c r="P5" t="n">
-        <v>137156937030</v>
+        <v>216256668300</v>
       </c>
       <c r="Q5" t="n">
-        <v>-560</v>
+        <v>-60</v>
       </c>
       <c r="R5" t="n">
-        <v>159425953630</v>
+        <v>234477845710</v>
       </c>
       <c r="S5" t="n">
         <v>41951673000</v>
       </c>
       <c r="T5" t="n">
-        <v>2963390000</v>
+        <v>2963389500</v>
       </c>
       <c r="U5" t="n">
-        <v>2963390000</v>
+        <v>2963389500</v>
       </c>
       <c r="V5" t="n">
-        <v>117016269800</v>
+        <v>99690002910</v>
       </c>
       <c r="W5" t="n">
-        <v>44569787010</v>
+        <v>31939387280</v>
       </c>
       <c r="X5" t="n">
         <v>10</v>
       </c>
       <c r="Y5" t="n">
-        <v>620820830</v>
+        <v>1330218500</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>284466260</v>
+        <v>1206872990</v>
       </c>
       <c r="AB5" t="n">
-        <v>40607907910</v>
+        <v>25860205980</v>
       </c>
       <c r="AC5" t="n">
-        <v>40607907910</v>
+        <v>25860205980</v>
       </c>
       <c r="AD5" t="n">
-        <v>3056592000</v>
+        <v>3542089800</v>
       </c>
       <c r="AE5" t="n">
-        <v>72446482790</v>
+        <v>67750615630</v>
       </c>
       <c r="AF5" t="n">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="AG5" t="n">
-        <v>10288561740</v>
+        <v>11449440180</v>
       </c>
       <c r="AH5" t="n">
-        <v>10288561740</v>
+        <v>11449440180</v>
       </c>
       <c r="AI5" t="n">
-        <v>293334860</v>
+        <v>87798880</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18968334810</v>
+        <v>25936488820</v>
       </c>
       <c r="AK5" t="n">
-        <v>1059892580</v>
+        <v>1463567360</v>
       </c>
       <c r="AL5" t="n">
-        <v>6365469920</v>
+        <v>10487924460</v>
       </c>
       <c r="AM5" t="n">
-        <v>11542972310</v>
+        <v>13984997000</v>
       </c>
       <c r="AN5" t="n">
-        <v>256982926230</v>
+        <v>320717498950</v>
       </c>
       <c r="AO5" t="n">
-        <v>121775431900</v>
+        <v>90959708520</v>
       </c>
       <c r="AP5" t="n">
-        <v>120</v>
+        <v>-640</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2474530210</v>
+        <v>6416180630</v>
       </c>
       <c r="AR5" t="n">
-        <v>1663763620</v>
+        <v>3360223170</v>
       </c>
       <c r="AS5" t="n">
-        <v>1219233130</v>
+        <v>1236365280</v>
       </c>
       <c r="AT5" t="n">
-        <v>1219233130</v>
+        <v>1236365280</v>
       </c>
       <c r="AU5" t="n">
-        <v>39758749000</v>
+        <v>34379857000</v>
       </c>
       <c r="AV5" t="n">
-        <v>26628254000</v>
+        <v>20224268000</v>
       </c>
       <c r="AW5" t="n">
-        <v>13130495000</v>
+        <v>14155589000</v>
       </c>
       <c r="AX5" t="n">
-        <v>56494905550</v>
+        <v>35650439130</v>
       </c>
       <c r="AY5" t="n">
-        <v>-32041564000</v>
+        <v>-45007409000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>88536470000</v>
+        <v>80657848000</v>
       </c>
       <c r="BA5" t="n">
-        <v>73308129000</v>
+        <v>73858929000</v>
       </c>
       <c r="BB5" t="n">
-        <v>15228341000</v>
+        <v>6798919000</v>
       </c>
       <c r="BC5" t="n">
-        <v>135207494320</v>
+        <v>229757790430</v>
       </c>
       <c r="BD5" t="n">
-        <v>1070</v>
+        <v>-330</v>
       </c>
       <c r="BE5" t="n">
-        <v>1188013670</v>
+        <v>3651935070</v>
       </c>
       <c r="BF5" t="n">
-        <v>24173170740</v>
+        <v>18583127000</v>
       </c>
       <c r="BG5" t="n">
-        <v>41670740000</v>
+        <v>40481461000</v>
       </c>
       <c r="BH5" t="n">
-        <v>-13404000</v>
+        <v>-66463000</v>
       </c>
       <c r="BI5" t="n">
-        <v>41684144000</v>
+        <v>40547924000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>68175568840</v>
+        <v>167041267690</v>
       </c>
       <c r="BK5" t="n">
-        <v>39835690460</v>
+        <v>144258200000</v>
       </c>
       <c r="BL5" t="n">
-        <v>28339878380</v>
+        <v>22783067690</v>
       </c>
       <c r="BM5" t="n">
-        <v>28339878000</v>
+        <v>22783068000</v>
       </c>
     </row>
   </sheetData>
@@ -2671,520 +2671,520 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>34737813030</v>
+        <v>41682554340</v>
       </c>
       <c r="C2" t="n">
-        <v>-11740512100</v>
+        <v>-4451726500</v>
       </c>
       <c r="D2" t="n">
-        <v>22783067690</v>
+        <v>28339878380</v>
       </c>
       <c r="E2" t="n">
-        <v>-10</v>
+        <v>290</v>
       </c>
       <c r="F2" t="n">
-        <v>33462842230</v>
+        <v>22619454720</v>
       </c>
       <c r="G2" t="n">
-        <v>948249910</v>
+        <v>504520900</v>
       </c>
       <c r="H2" t="n">
-        <v>-11628024440</v>
+        <v>5215902470</v>
       </c>
       <c r="I2" t="n">
-        <v>-18963437860</v>
+        <v>-13558553370</v>
       </c>
       <c r="J2" t="n">
-        <v>2489000</v>
+        <v>1310000</v>
       </c>
       <c r="K2" t="n">
-        <v>-9482846400</v>
+        <v>-2963389500</v>
       </c>
       <c r="L2" t="n">
-        <v>-39142911710</v>
+        <v>-27359825000</v>
       </c>
       <c r="M2" t="n">
-        <v>-180789770</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>677776940</v>
+      </c>
+      <c r="N2" t="n">
+        <v>261788960</v>
+      </c>
       <c r="O2" t="n">
-        <v>-27242877590</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
+        <v>-23867613170</v>
+      </c>
+      <c r="P2" t="n">
+        <v>38514943550</v>
+      </c>
       <c r="Q2" t="n">
-        <v>-27242877590</v>
+        <v>-62382556720</v>
       </c>
       <c r="R2" t="n">
-        <v>-11190116560</v>
+        <v>-3407449650</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>-11190116560</v>
+        <v>-3407449650</v>
       </c>
       <c r="U2" t="n">
-        <v>-529127790</v>
+        <v>-1024328080</v>
       </c>
       <c r="V2" t="n">
-        <v>21267750</v>
+        <v>19948770</v>
       </c>
       <c r="W2" t="n">
-        <v>-550395540</v>
+        <v>-1044276850</v>
       </c>
       <c r="X2" t="n">
-        <v>46478325130</v>
+        <v>46134280840</v>
       </c>
       <c r="Y2" t="n">
-        <v>-11833223620</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>5462898730</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-1354183660</v>
-      </c>
+        <v>-2513082120</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>-8933260000</v>
+        <v>-3368418000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-3640029000</v>
+        <v>-6288211000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-897739000</v>
+        <v>2044841000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-9127450000</v>
+        <v>10653946000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1275015000</v>
+        <v>-403790000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-1362597000</v>
+        <v>81476000</v>
       </c>
       <c r="AH2" t="n">
-        <v>7498477000</v>
+        <v>-9436539000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-4363492000</v>
+        <v>130895000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>8221000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>11231970000</v>
-      </c>
+        <v>-119992000</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>20042220000</v>
+        <v>20245627000</v>
       </c>
       <c r="AM2" t="n">
-        <v>8800551000</v>
+        <v>7075527000</v>
       </c>
       <c r="AN2" t="n">
-        <v>11241669000</v>
+        <v>13170100000</v>
       </c>
       <c r="AO2" t="n">
-        <v>4636133000</v>
+        <v>5117071000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-5363000</v>
+        <v>-4598000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>59474000</v>
+        <v>2960000</v>
       </c>
       <c r="AR2" t="n">
-        <v>13614000</v>
+        <v>21490000</v>
       </c>
       <c r="AS2" t="n">
-        <v>31513317000</v>
+        <v>27004832000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>56775321670</v>
+        <v>48216636610</v>
       </c>
       <c r="C3" t="n">
-        <v>-2591554120</v>
+        <v>-2749992700</v>
       </c>
       <c r="D3" t="n">
-        <v>33462842230</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>34267163100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
       <c r="F3" t="n">
-        <v>34267163100</v>
+        <v>28339878380</v>
       </c>
       <c r="G3" t="n">
-        <v>131625300</v>
+        <v>380706200</v>
       </c>
       <c r="H3" t="n">
-        <v>-935946170</v>
+        <v>5546578510</v>
       </c>
       <c r="I3" t="n">
-        <v>-12829770590</v>
+        <v>-14138517280</v>
       </c>
       <c r="J3" t="n">
-        <v>2060100</v>
+        <v>1343000</v>
       </c>
       <c r="K3" t="n">
-        <v>-4741423200</v>
+        <v>-3556067400</v>
       </c>
       <c r="L3" t="n">
-        <v>-47473051370</v>
+        <v>-31281533520</v>
       </c>
       <c r="M3" t="n">
-        <v>542686230</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>175660790</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1089243720</v>
+      </c>
       <c r="O3" t="n">
-        <v>-45462115140</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
+        <v>-29806168330</v>
+      </c>
+      <c r="P3" t="n">
+        <v>61749946970</v>
+      </c>
       <c r="Q3" t="n">
-        <v>-45462115140</v>
+        <v>-29806168330</v>
       </c>
       <c r="R3" t="n">
-        <v>-1654236610</v>
-      </c>
-      <c r="S3" t="n">
-        <v>28600000</v>
-      </c>
+        <v>-2127877920</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>-1682836610</v>
+        <v>-2127877920</v>
       </c>
       <c r="U3" t="n">
-        <v>-899385850</v>
+        <v>-612391780</v>
       </c>
       <c r="V3" t="n">
-        <v>9331660</v>
+        <v>9723000</v>
       </c>
       <c r="W3" t="n">
-        <v>-908717510</v>
+        <v>-622114780</v>
       </c>
       <c r="X3" t="n">
-        <v>59366875790</v>
+        <v>50966629310</v>
       </c>
       <c r="Y3" t="n">
-        <v>-10447587840</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2277124710</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-1572693670</v>
-      </c>
+        <v>-7827890980</v>
+      </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>6934693000</v>
+        <v>-7450462000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1117000000</v>
+        <v>-13600000000</v>
       </c>
       <c r="AD3" t="n">
-        <v>398921000</v>
+        <v>-4873624000</v>
       </c>
       <c r="AE3" t="n">
-        <v>560611000</v>
+        <v>-1942634000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-3960953000</v>
+        <v>2363639000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-886235000</v>
+        <v>123842000</v>
       </c>
       <c r="AH3" t="n">
-        <v>11941649000</v>
+        <v>10482946000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-2312340000</v>
+        <v>-601473000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>72133000</v>
+        <v>-94130000</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>18524512000</v>
+        <v>20739084000</v>
       </c>
       <c r="AM3" t="n">
-        <v>6851844000</v>
+        <v>7229971000</v>
       </c>
       <c r="AN3" t="n">
-        <v>11672668000</v>
+        <v>13509113000</v>
       </c>
       <c r="AO3" t="n">
-        <v>3669824000</v>
+        <v>5080112000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-5733000</v>
+        <v>-6036000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-41971000</v>
+        <v>-103310000</v>
       </c>
       <c r="AR3" t="n">
-        <v>44481000</v>
+        <v>-195297000</v>
       </c>
       <c r="AS3" t="n">
-        <v>42224433000</v>
+        <v>41426032000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>48216636610</v>
+        <v>56775321670</v>
       </c>
       <c r="C4" t="n">
-        <v>-2749992700</v>
+        <v>-2591554120</v>
       </c>
       <c r="D4" t="n">
+        <v>33462842230</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
         <v>34267163100</v>
       </c>
-      <c r="E4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F4" t="n">
-        <v>28339878380</v>
-      </c>
       <c r="G4" t="n">
-        <v>380706200</v>
+        <v>131625300</v>
       </c>
       <c r="H4" t="n">
-        <v>5546578510</v>
+        <v>-935946170</v>
       </c>
       <c r="I4" t="n">
-        <v>-14138517280</v>
+        <v>-12829770590</v>
       </c>
       <c r="J4" t="n">
-        <v>1343000</v>
+        <v>2060100</v>
       </c>
       <c r="K4" t="n">
-        <v>-3556067400</v>
+        <v>-4741423200</v>
       </c>
       <c r="L4" t="n">
-        <v>-31281533520</v>
+        <v>-47473051370</v>
       </c>
       <c r="M4" t="n">
-        <v>175660790</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1089243720</v>
-      </c>
+        <v>542686230</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>-29806168330</v>
-      </c>
-      <c r="P4" t="n">
-        <v>61749946970</v>
-      </c>
+        <v>-45462115140</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>-29806168330</v>
+        <v>-45462115140</v>
       </c>
       <c r="R4" t="n">
-        <v>-2127877920</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
+        <v>-1654236610</v>
+      </c>
+      <c r="S4" t="n">
+        <v>28600000</v>
+      </c>
       <c r="T4" t="n">
-        <v>-2127877920</v>
+        <v>-1682836610</v>
       </c>
       <c r="U4" t="n">
-        <v>-612391780</v>
+        <v>-899385850</v>
       </c>
       <c r="V4" t="n">
-        <v>9723000</v>
+        <v>9331660</v>
       </c>
       <c r="W4" t="n">
-        <v>-622114780</v>
+        <v>-908717510</v>
       </c>
       <c r="X4" t="n">
-        <v>50966629310</v>
+        <v>59366875790</v>
       </c>
       <c r="Y4" t="n">
-        <v>-7827890980</v>
-      </c>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
+        <v>-10447587840</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2277124710</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-1572693670</v>
+      </c>
       <c r="AB4" t="n">
-        <v>-7450462000</v>
+        <v>6934693000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-13600000000</v>
+        <v>-1117000000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-4873624000</v>
+        <v>398921000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-1942634000</v>
+        <v>560611000</v>
       </c>
       <c r="AF4" t="n">
-        <v>2363639000</v>
+        <v>-3960953000</v>
       </c>
       <c r="AG4" t="n">
-        <v>123842000</v>
+        <v>-886235000</v>
       </c>
       <c r="AH4" t="n">
-        <v>10482946000</v>
+        <v>11941649000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-601473000</v>
+        <v>-2312340000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-94130000</v>
+        <v>72133000</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>20739084000</v>
+        <v>18524512000</v>
       </c>
       <c r="AM4" t="n">
-        <v>7229971000</v>
+        <v>6851844000</v>
       </c>
       <c r="AN4" t="n">
-        <v>13509113000</v>
+        <v>11672668000</v>
       </c>
       <c r="AO4" t="n">
-        <v>5080112000</v>
+        <v>3669824000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-6036000</v>
+        <v>-5733000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-103310000</v>
+        <v>-41971000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-195297000</v>
+        <v>44481000</v>
       </c>
       <c r="AS4" t="n">
-        <v>41426032000</v>
+        <v>42224433000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>41682554340</v>
+        <v>34737813030</v>
       </c>
       <c r="C5" t="n">
-        <v>-4451726500</v>
+        <v>-11740512100</v>
       </c>
       <c r="D5" t="n">
-        <v>28339878380</v>
+        <v>22783067690</v>
       </c>
       <c r="E5" t="n">
-        <v>290</v>
+        <v>-10</v>
       </c>
       <c r="F5" t="n">
-        <v>22619454720</v>
+        <v>33462842230</v>
       </c>
       <c r="G5" t="n">
-        <v>504520900</v>
+        <v>948249910</v>
       </c>
       <c r="H5" t="n">
-        <v>5215902470</v>
+        <v>-11628024440</v>
       </c>
       <c r="I5" t="n">
-        <v>-13558553370</v>
+        <v>-18963437860</v>
       </c>
       <c r="J5" t="n">
-        <v>1310000</v>
+        <v>2489000</v>
       </c>
       <c r="K5" t="n">
-        <v>-2963389500</v>
+        <v>-9482846400</v>
       </c>
       <c r="L5" t="n">
-        <v>-27359825000</v>
+        <v>-39142911710</v>
       </c>
       <c r="M5" t="n">
-        <v>677776940</v>
-      </c>
-      <c r="N5" t="n">
-        <v>261788960</v>
-      </c>
+        <v>-180789770</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>-23867613170</v>
-      </c>
-      <c r="P5" t="n">
-        <v>38514943550</v>
-      </c>
+        <v>-27242877590</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>-62382556720</v>
+        <v>-27242877590</v>
       </c>
       <c r="R5" t="n">
-        <v>-3407449650</v>
+        <v>-11190116560</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>-3407449650</v>
+        <v>-11190116560</v>
       </c>
       <c r="U5" t="n">
-        <v>-1024328080</v>
+        <v>-529127790</v>
       </c>
       <c r="V5" t="n">
-        <v>19948770</v>
+        <v>21267750</v>
       </c>
       <c r="W5" t="n">
-        <v>-1044276850</v>
+        <v>-550395540</v>
       </c>
       <c r="X5" t="n">
-        <v>46134280840</v>
+        <v>46478325130</v>
       </c>
       <c r="Y5" t="n">
-        <v>-2513082120</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
+        <v>-11833223620</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5462898730</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-1354183660</v>
+      </c>
       <c r="AB5" t="n">
-        <v>-3368418000</v>
+        <v>-8933260000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-6288211000</v>
+        <v>-3640029000</v>
       </c>
       <c r="AD5" t="n">
-        <v>2044841000</v>
+        <v>-897739000</v>
       </c>
       <c r="AE5" t="n">
-        <v>10653946000</v>
+        <v>-9127450000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-403790000</v>
+        <v>-1275015000</v>
       </c>
       <c r="AG5" t="n">
-        <v>81476000</v>
+        <v>-1362597000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-9436539000</v>
+        <v>7498477000</v>
       </c>
       <c r="AI5" t="n">
-        <v>130895000</v>
+        <v>-4363492000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-119992000</v>
-      </c>
-      <c r="AK5" t="inlineStr"/>
+        <v>8221000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>11231970000</v>
+      </c>
       <c r="AL5" t="n">
-        <v>20245627000</v>
+        <v>20042220000</v>
       </c>
       <c r="AM5" t="n">
-        <v>7075527000</v>
+        <v>8800551000</v>
       </c>
       <c r="AN5" t="n">
-        <v>13170100000</v>
+        <v>11241669000</v>
       </c>
       <c r="AO5" t="n">
-        <v>5117071000</v>
+        <v>4636133000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-4598000</v>
+        <v>-5363000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2960000</v>
+        <v>59474000</v>
       </c>
       <c r="AR5" t="n">
-        <v>21490000</v>
+        <v>13614000</v>
       </c>
       <c r="AS5" t="n">
-        <v>27004832000</v>
+        <v>31513317000</v>
       </c>
     </row>
   </sheetData>
@@ -3404,187 +3404,187 @@
       </c>
       <c r="AO1" t="inlineStr">
         <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
           <t>sharesOutstanding</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>impliedSharesOutstanding</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="BB1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="BF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="BG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="BH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="BO1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="BP1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="BQ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="BR1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="BS1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="BT1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="BU1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="BV1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="BY1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
@@ -3601,49 +3601,49 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>24750</v>
+        <v>24250</v>
       </c>
       <c r="D2" t="n">
-        <v>24700</v>
+        <v>24400</v>
       </c>
       <c r="E2" t="n">
-        <v>24200</v>
+        <v>23500</v>
       </c>
       <c r="F2" t="n">
-        <v>25150</v>
+        <v>24400</v>
       </c>
       <c r="G2" t="n">
-        <v>24750</v>
+        <v>24250</v>
       </c>
       <c r="H2" t="n">
-        <v>24700</v>
+        <v>24400</v>
       </c>
       <c r="I2" t="n">
-        <v>24200</v>
+        <v>23500</v>
       </c>
       <c r="J2" t="n">
-        <v>25150</v>
+        <v>24400</v>
       </c>
       <c r="K2" t="n">
-        <v>12392</v>
+        <v>818</v>
       </c>
       <c r="L2" t="n">
-        <v>12392</v>
+        <v>818</v>
       </c>
       <c r="M2" t="n">
-        <v>14683</v>
+        <v>13230</v>
       </c>
       <c r="N2" t="n">
-        <v>12729</v>
+        <v>7627</v>
       </c>
       <c r="O2" t="n">
-        <v>12729</v>
+        <v>7627</v>
       </c>
       <c r="P2" t="n">
-        <v>25100</v>
+        <v>23500</v>
       </c>
       <c r="Q2" t="n">
-        <v>25150</v>
+        <v>23600</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -3652,13 +3652,13 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>149058486272</v>
+        <v>139279302656</v>
       </c>
       <c r="U2" t="n">
-        <v>146687780250</v>
+        <v>145502424450</v>
       </c>
       <c r="V2" t="n">
-        <v>24200</v>
+        <v>23300</v>
       </c>
       <c r="W2" t="n">
         <v>37000</v>
@@ -3670,10 +3670,10 @@
         <v>18200</v>
       </c>
       <c r="Z2" t="n">
-        <v>27570</v>
+        <v>26785</v>
       </c>
       <c r="AA2" t="n">
-        <v>30556.25</v>
+        <v>30030</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="AE2" t="n">
-        <v>25150</v>
+        <v>23500</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -3734,138 +3734,138 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="AO2" t="n">
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1163635200000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-750</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>23500.0 - 24400.0</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>13230</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>200</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.008583690999999999</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>23300.0 - 37000.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>-13500</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-0.36486486</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-29.65616</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1754996340</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1755518400</v>
+      </c>
+      <c r="BC2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>Multicampus</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BF2" t="n">
+        <v>1782175100</v>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>KOE</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>Asia/Seoul</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>KST</t>
+        </is>
+      </c>
+      <c r="BJ2" t="n">
+        <v>32400000</v>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>kr_market</t>
+        </is>
+      </c>
+      <c r="BL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM2" t="n">
         <v>5926779</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="BN2" t="n">
         <v>5926779</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>-2420</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-0.08777657</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-5406.25</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>-0.17692779</v>
-      </c>
-      <c r="AU2" t="n">
+      <c r="BO2" t="n">
+        <v>-3285</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>-0.12264327</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>-6530</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>-0.21744922</v>
+      </c>
+      <c r="BS2" t="n">
         <v>20</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="BT2" t="n">
         <v>20</v>
       </c>
-      <c r="AW2" t="b">
+      <c r="BU2" t="b">
         <v>0</v>
       </c>
-      <c r="AX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1163635200000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>400</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>24200.0 - 25150.0</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>14683</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>950</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0.0392562</v>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>24200.0 - 37000.0</t>
-        </is>
-      </c>
-      <c r="BG2" t="n">
-        <v>-11850</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>-0.32027027</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>-26.557863</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1754996340</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1755518400</v>
-      </c>
-      <c r="BL2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>Multicampus Corporation</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="BN2" t="n">
-        <v>1780381830</v>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>KOE</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>Asia/Seoul</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>KST</t>
-        </is>
-      </c>
-      <c r="BR2" t="n">
-        <v>32400000</v>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>kr_market</t>
-        </is>
-      </c>
-      <c r="BT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>Multicampus</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>Multicampus Corporation</t>
-        </is>
-      </c>
-      <c r="BW2" t="n">
-        <v>1.6161617</v>
-      </c>
       <c r="BX2" t="n">
-        <v>25150</v>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
+        <v>-3.0927835</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>23500</v>
       </c>
       <c r="BZ2" t="inlineStr"/>
     </row>
